--- a/Test_Cases/02_Navigation/Navigation_Test_Cases.xlsx
+++ b/Test_Cases/02_Navigation/Navigation_Test_Cases.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="256">
   <si>
     <t>Application URL:</t>
   </si>
@@ -845,6 +845,36 @@
     <t>Selected Chapter and Topic remain active.</t>
   </si>
   <si>
+    <t>TC-NAV-COMPLETE</t>
+  </si>
+  <si>
+    <t>Complete flow: class popup default tab, tab switching, Grade/Division/Subject, Chapter/Topic in one run</t>
+  </si>
+  <si>
+    <t>End-to-end navigation session</t>
+  </si>
+  <si>
+    <t>Logged in</t>
+  </si>
+  <si>
+    <t>Class 8 / A / Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the Class popup, confirm Recent Classes is the default active tab.
+2. Switch to All My Classes.
+3. Select Grade, Division, Subject.
+4. Confirm Current Class updates.
+5. Open Chapters popup, select a Chapter.
+6. Select a Topic.
+7. Confirm the Chapter/Topic control reflects the new selection.</t>
+  </si>
+  <si>
+    <t>Each step's outcome matches the individually-tested behavior (TC-NAV-002, TC-NAV-028, TC-NAV-029) when chained together in one continuous session.</t>
+  </si>
+  <si>
+    <t>Class and Chapter/Topic changed to the values selected during the test.</t>
+  </si>
+  <si>
     <t>Execution Status</t>
   </si>
   <si>
@@ -864,6 +894,21 @@
   </si>
   <si>
     <t>Not Executed</t>
+  </si>
+  <si>
+    <t>Automated - Passing</t>
+  </si>
+  <si>
+    <t>Passes live (isolated run, 2026-08-23)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
   </si>
 </sst>
 </file>
@@ -927,7 +972,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -935,6 +980,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1245,7 +1293,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2318,6 +2366,41 @@
         <v>235</v>
       </c>
     </row>
+    <row r="33" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K30"/>
   <hyperlinks>
@@ -2332,7 +2415,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2354,29 +2437,29 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>241</v>
+      <c r="C3" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2387,7 +2470,7 @@
         <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -2403,7 +2486,7 @@
         <v>25</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -2419,7 +2502,7 @@
         <v>34</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -2435,7 +2518,7 @@
         <v>40</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -2451,7 +2534,7 @@
         <v>48</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -2467,7 +2550,7 @@
         <v>56</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -2483,7 +2566,7 @@
         <v>62</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -2499,7 +2582,7 @@
         <v>68</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -2515,7 +2598,7 @@
         <v>76</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -2531,7 +2614,7 @@
         <v>83</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -2547,7 +2630,7 @@
         <v>91</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -2563,7 +2646,7 @@
         <v>99</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -2579,7 +2662,7 @@
         <v>107</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -2595,7 +2678,7 @@
         <v>115</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -2611,7 +2694,7 @@
         <v>123</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -2627,7 +2710,7 @@
         <v>128</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -2643,7 +2726,7 @@
         <v>136</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -2659,7 +2742,7 @@
         <v>143</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -2675,7 +2758,7 @@
         <v>150</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -2691,7 +2774,7 @@
         <v>158</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -2707,7 +2790,7 @@
         <v>165</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -2723,7 +2806,7 @@
         <v>173</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -2739,7 +2822,7 @@
         <v>182</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -2755,7 +2838,7 @@
         <v>189</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -2771,7 +2854,7 @@
         <v>197</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -2787,7 +2870,7 @@
         <v>205</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -2803,7 +2886,7 @@
         <v>213</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -2819,7 +2902,7 @@
         <v>222</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -2835,13 +2918,42 @@
         <v>230</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>253</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H30"/>
